--- a/CPL.xlsx
+++ b/CPL.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="175">
   <si>
     <t xml:space="preserve">Designator</t>
   </si>
@@ -235,7 +235,7 @@
     <t xml:space="preserve">J3</t>
   </si>
   <si>
-    <t xml:space="preserve">69.30</t>
+    <t xml:space="preserve">73.79</t>
   </si>
   <si>
     <t xml:space="preserve">36.51</t>
@@ -310,46 +310,52 @@
     <t xml:space="preserve">63.18</t>
   </si>
   <si>
+    <t xml:space="preserve">35.56</t>
+  </si>
+  <si>
     <t xml:space="preserve">R7</t>
   </si>
   <si>
+    <t xml:space="preserve">37.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R13</t>
+  </si>
+  <si>
     <t xml:space="preserve">37.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R13</t>
   </si>
   <si>
     <t xml:space="preserve">20.96</t>
@@ -1485,11 +1491,11 @@
       <c r="A43" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>72</v>
+      <c r="C43" s="0" t="s">
+        <v>96</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>8</v>
@@ -1500,13 +1506,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B44" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>97</v>
+      <c r="C44" s="0" t="s">
+        <v>98</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>8</v>
@@ -1517,13 +1523,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>8</v>
@@ -1534,13 +1540,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>8</v>
@@ -1551,7 +1557,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>41</v>
@@ -1568,13 +1574,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>8</v>
@@ -1585,13 +1591,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>8</v>
@@ -1602,13 +1608,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>8</v>
@@ -1619,13 +1625,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>8</v>
@@ -1636,13 +1642,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>8</v>
@@ -1653,13 +1659,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>8</v>
@@ -1670,13 +1676,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>8</v>
@@ -1687,13 +1693,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>8</v>
@@ -1704,13 +1710,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>8</v>
@@ -1721,13 +1727,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>8</v>
@@ -1738,13 +1744,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>8</v>
@@ -1755,13 +1761,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>8</v>
@@ -1772,13 +1778,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>8</v>
@@ -1789,13 +1795,13 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>8</v>
@@ -1806,13 +1812,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>8</v>
@@ -1823,13 +1829,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>8</v>
@@ -1840,13 +1846,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>8</v>
@@ -1857,13 +1863,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>8</v>
@@ -1874,13 +1880,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>8</v>
@@ -1891,13 +1897,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>8</v>
@@ -1908,13 +1914,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>8</v>
@@ -1925,13 +1931,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>8</v>
@@ -1942,13 +1948,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>8</v>
@@ -1959,13 +1965,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>8</v>
@@ -1976,13 +1982,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>8</v>
@@ -1993,13 +1999,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>8</v>
@@ -2010,13 +2016,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>8</v>
@@ -2027,13 +2033,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>8</v>
@@ -2044,13 +2050,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>8</v>
@@ -2061,13 +2067,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>8</v>
@@ -2078,13 +2084,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>8</v>
@@ -2095,13 +2101,13 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>8</v>
@@ -2112,13 +2118,13 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>8</v>
@@ -2129,13 +2135,13 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>8</v>
@@ -2146,13 +2152,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>8</v>
@@ -2163,13 +2169,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>8</v>
